--- a/08_tables/q8_within_full_correlation_matrix_with_trend_lags.xlsx
+++ b/08_tables/q8_within_full_correlation_matrix_with_trend_lags.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q8_within_full_correlation_matrix_with_trend_lags.xlsx
+++ b/08_tables/q8_within_full_correlation_matrix_with_trend_lags.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,134 +417,134 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>i_within</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P_within</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W_within</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>WR_within</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>GDP_within</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LS_within</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>UN_within</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SHORTUN_within</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>LONGUN_within</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>LF_within</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>REER_within</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>SH_within</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>trend_within</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>i_lag1_within</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P_lag1_within</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>W_lag1_within</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>WR_lag1_within</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>GDP_lag1_within</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LS_lag1_within</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UN_lag1_within</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>SHORTUN_lag1_within</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>LONGUN_lag1_within</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>LF_lag1_within</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>REER_lag1_within</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SH_lag1_within</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>i_within</t>
         </is>
@@ -568,7 +556,7 @@
         <v>-0.7159298227120567</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7269491885805053</v>
+        <v>-0.7269491885805052</v>
       </c>
       <c r="E2" t="n">
         <v>-0.1048890640785549</v>
@@ -577,7 +565,7 @@
         <v>-0.3450090371264747</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5467885309571058</v>
+        <v>0.5467885309571057</v>
       </c>
       <c r="H2" t="n">
         <v>-0.1201281343384327</v>
@@ -595,10 +583,10 @@
         <v>-0.1024043659453598</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9787963686249099</v>
+        <v>0.9787963686249103</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7399368851371887</v>
+        <v>-0.7399368851371885</v>
       </c>
       <c r="O2" t="n">
         <v>0.9197151451857176</v>
@@ -607,7 +595,7 @@
         <v>-0.7480039915943725</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7410177579100143</v>
+        <v>-0.7410177579100142</v>
       </c>
       <c r="R2" t="n">
         <v>-0.0344189024565565</v>
@@ -616,7 +604,7 @@
         <v>-0.3485719395286916</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5665057825466118</v>
+        <v>0.566505782546612</v>
       </c>
       <c r="U2" t="n">
         <v>-0.183496321026466</v>
@@ -631,14 +619,14 @@
         <v>-0.3523125450335107</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1085412725392239</v>
+        <v>-0.1085412725392238</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9109655048595507</v>
+        <v>0.9109655048595505</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>P_within</t>
         </is>
@@ -659,10 +647,10 @@
         <v>0.4751622737830543</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7457110057737747</v>
+        <v>-0.7457110057737745</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3631279539822986</v>
+        <v>0.3631279539822987</v>
       </c>
       <c r="I3" t="n">
         <v>0.2338806729579787</v>
@@ -674,34 +662,34 @@
         <v>0.5077454095735964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1004251385788368</v>
+        <v>0.1004251385788369</v>
       </c>
       <c r="M3" t="n">
         <v>-0.728801119542662</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9715445987291108</v>
+        <v>0.9715445987291107</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6910013869912225</v>
+        <v>-0.6910013869912226</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9992334893105516</v>
+        <v>0.9992334893105513</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9380683044644278</v>
+        <v>0.9380683044644277</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2046524560409182</v>
+        <v>-0.2046524560409183</v>
       </c>
       <c r="S3" t="n">
         <v>0.4749741804118587</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7461294287412867</v>
+        <v>-0.7461294287412865</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3805927874327037</v>
+        <v>0.3805927874327036</v>
       </c>
       <c r="V3" t="n">
         <v>0.2530410743735391</v>
@@ -710,23 +698,23 @@
         <v>0.2105054754792068</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5060389634123369</v>
+        <v>0.5060389634123368</v>
       </c>
       <c r="Y3" t="n">
         <v>0.1022002569754112</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7050554225057321</v>
+        <v>-0.7050554225057319</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>W_within</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7269491885805053</v>
+        <v>-0.7269491885805052</v>
       </c>
       <c r="C4" t="n">
         <v>0.9395751093951566</v>
@@ -735,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05962418574781018</v>
+        <v>0.05962418574781016</v>
       </c>
       <c r="F4" t="n">
         <v>0.5355704500963318</v>
@@ -744,7 +732,7 @@
         <v>-0.6564256274469835</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2554397836759314</v>
+        <v>0.2554397836759315</v>
       </c>
       <c r="I4" t="n">
         <v>0.196626909839874</v>
@@ -759,22 +747,22 @@
         <v>0.005108225149678319</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7592871856560741</v>
+        <v>-0.7592871856560743</v>
       </c>
       <c r="N4" t="n">
         <v>0.9773789413615545</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7168417244309265</v>
+        <v>-0.7168417244309264</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9385846196643306</v>
+        <v>0.9385846196643308</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9990738433927511</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04505610243589216</v>
+        <v>0.04505610243589214</v>
       </c>
       <c r="S4" t="n">
         <v>0.537635761637595</v>
@@ -786,7 +774,7 @@
         <v>0.2753731258369863</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22826504286999</v>
+        <v>0.2282650428699901</v>
       </c>
       <c r="W4" t="n">
         <v>0.2263371106962513</v>
@@ -795,14 +783,14 @@
         <v>0.5488741722992444</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01752667053921757</v>
+        <v>0.01752667053921759</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.7474713554899223</v>
+        <v>-0.7474713554899222</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WR_within</t>
         </is>
@@ -814,7 +802,7 @@
         <v>-0.1802732996605594</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05962418574781018</v>
+        <v>0.05962418574781016</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -835,16 +823,16 @@
         <v>0.1404645209183138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1459523177759164</v>
+        <v>0.1459523177759163</v>
       </c>
       <c r="L5" t="n">
         <v>-0.1701723987384076</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1140672766905316</v>
+        <v>-0.1140672766905315</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0437052829348609</v>
+        <v>-0.04370528293486092</v>
       </c>
       <c r="O5" t="n">
         <v>-0.154743663702222</v>
@@ -853,10 +841,10 @@
         <v>-0.157581973292429</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07168818355430046</v>
+        <v>0.07168818355430047</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9826798363442868</v>
+        <v>0.9826798363442869</v>
       </c>
       <c r="S5" t="n">
         <v>0.1464936116249397</v>
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>GDP_within</t>
         </is>
@@ -908,10 +896,10 @@
         <v>-0.272747974351208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03775576359132887</v>
+        <v>0.03775576359132885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1579411112103675</v>
+        <v>0.1579411112103674</v>
       </c>
       <c r="J6" t="n">
         <v>0.3913772962472417</v>
@@ -923,13 +911,13 @@
         <v>0.12874803740802</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3548747588492231</v>
+        <v>-0.354874758849223</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5082235787439886</v>
+        <v>0.5082235787439884</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3476005160648407</v>
+        <v>-0.3476005160648406</v>
       </c>
       <c r="P6" t="n">
         <v>0.472863168837059</v>
@@ -941,7 +929,7 @@
         <v>0.1312563999114845</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9984926731230138</v>
+        <v>0.9984926731230139</v>
       </c>
       <c r="T6" t="n">
         <v>-0.270889983805397</v>
@@ -950,7 +938,7 @@
         <v>0.05200941674030939</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2113956695133399</v>
+        <v>0.21139566951334</v>
       </c>
       <c r="W6" t="n">
         <v>0.4222035334338685</v>
@@ -959,23 +947,23 @@
         <v>0.9629063337248143</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1242403715666645</v>
+        <v>0.1242403715666644</v>
       </c>
       <c r="Z6" t="n">
         <v>-0.3610523888498124</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>LS_within</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5467885309571058</v>
+        <v>0.5467885309571057</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7457110057737747</v>
+        <v>-0.7457110057737745</v>
       </c>
       <c r="D7" t="n">
         <v>-0.6564256274469835</v>
@@ -1002,16 +990,16 @@
         <v>-0.2844560395342247</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05082317139641967</v>
+        <v>-0.0508231713964197</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5531083869641533</v>
+        <v>0.5531083869641534</v>
       </c>
       <c r="N7" t="n">
         <v>-0.7308397985224826</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5249199428257839</v>
+        <v>0.5249199428257838</v>
       </c>
       <c r="P7" t="n">
         <v>-0.7514365973597997</v>
@@ -1020,19 +1008,19 @@
         <v>-0.6611129902486281</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4424657956539679</v>
+        <v>0.442465795653968</v>
       </c>
       <c r="S7" t="n">
         <v>-0.2713902907614898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9523127648794044</v>
+        <v>0.9523127648794043</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.390925988115669</v>
+        <v>-0.3909259881156689</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2077225269364404</v>
+        <v>-0.2077225269364405</v>
       </c>
       <c r="W7" t="n">
         <v>-0.2791035806409053</v>
@@ -1048,7 +1036,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UN_within</t>
         </is>
@@ -1057,16 +1045,16 @@
         <v>-0.1201281343384327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3631279539822986</v>
+        <v>0.3631279539822987</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2554397836759314</v>
+        <v>0.2554397836759315</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2286812664293737</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03775576359132887</v>
+        <v>0.03775576359132885</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2940039962134414</v>
@@ -1081,19 +1069,19 @@
         <v>0.522846792408085</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06958197744242318</v>
+        <v>0.06958197744242317</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03354948048175851</v>
+        <v>-0.03354948048175853</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1140369328089865</v>
+        <v>-0.1140369328089864</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3020017191253656</v>
+        <v>0.3020017191253655</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.01847722106656332</v>
+        <v>-0.01847722106656333</v>
       </c>
       <c r="P8" t="n">
         <v>0.335192587953228</v>
@@ -1105,7 +1093,7 @@
         <v>-0.2202120339728879</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0271662516839218</v>
+        <v>0.02716625168392179</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1998627058426368</v>
@@ -1123,14 +1111,14 @@
         <v>0.05846979739506657</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.014878133535407</v>
+        <v>0.01487813353540698</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.01975413508918413</v>
+        <v>-0.01975413508918411</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SHORTUN_within</t>
         </is>
@@ -1148,7 +1136,7 @@
         <v>0.07770161498229941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1579411112103675</v>
+        <v>0.1579411112103674</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1590911790493302</v>
@@ -1163,7 +1151,7 @@
         <v>0.5948183975702254</v>
       </c>
       <c r="K9" t="n">
-        <v>0.286708439927226</v>
+        <v>0.2867084399272259</v>
       </c>
       <c r="L9" t="n">
         <v>0.005970193834536096</v>
@@ -1172,7 +1160,7 @@
         <v>-0.1900798992435649</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2203872848496002</v>
+        <v>0.2203872848496001</v>
       </c>
       <c r="O9" t="n">
         <v>-0.1145316919028703</v>
@@ -1181,38 +1169,38 @@
         <v>0.2203072655079454</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.179114032050075</v>
+        <v>0.1791140320500751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05914136800731865</v>
+        <v>0.05914136800731867</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1350122444071746</v>
+        <v>0.1350122444071745</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1241029135023845</v>
+        <v>-0.1241029135023844</v>
       </c>
       <c r="U9" t="n">
         <v>0.2092184057219418</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7965892936420816</v>
+        <v>0.796589293642082</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3853032059775952</v>
+        <v>0.3853032059775953</v>
       </c>
       <c r="X9" t="n">
         <v>0.2503547096546833</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01288808054943055</v>
+        <v>0.01288808054943057</v>
       </c>
       <c r="Z9" t="n">
         <v>-0.1206258957207637</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>LONGUN_within</t>
         </is>
@@ -1248,7 +1236,7 @@
         <v>0.4095238994399639</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.02545801417043</v>
+        <v>-0.02545801417043001</v>
       </c>
       <c r="M10" t="n">
         <v>-0.160792026307141</v>
@@ -1257,7 +1245,7 @@
         <v>0.1997287231143273</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1254979587604979</v>
+        <v>-0.125497958760498</v>
       </c>
       <c r="P10" t="n">
         <v>0.1942477236129076</v>
@@ -1278,7 +1266,7 @@
         <v>0.5001773505693666</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6757077905928681</v>
+        <v>0.675707790592868</v>
       </c>
       <c r="W10" t="n">
         <v>0.9018633145039019</v>
@@ -1287,14 +1275,14 @@
         <v>0.4157275141378775</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003373045331640988</v>
+        <v>0.003373045331640987</v>
       </c>
       <c r="Z10" t="n">
         <v>-0.1249004035366156</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>LF_within</t>
         </is>
@@ -1309,7 +1297,7 @@
         <v>0.5491448211661821</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1459523177759164</v>
+        <v>0.1459523177759163</v>
       </c>
       <c r="F11" t="n">
         <v>0.9634088380644662</v>
@@ -1318,10 +1306,10 @@
         <v>-0.2844560395342247</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06958197744242318</v>
+        <v>0.06958197744242317</v>
       </c>
       <c r="I11" t="n">
-        <v>0.286708439927226</v>
+        <v>0.2867084399272259</v>
       </c>
       <c r="J11" t="n">
         <v>0.4095238994399639</v>
@@ -1330,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1279613376987077</v>
+        <v>0.1279613376987078</v>
       </c>
       <c r="M11" t="n">
         <v>-0.3534845838879406</v>
@@ -1363,7 +1351,7 @@
         <v>0.3174167359269896</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4164659717263127</v>
+        <v>0.4164659717263126</v>
       </c>
       <c r="X11" t="n">
         <v>0.9975287621035562</v>
@@ -1372,11 +1360,11 @@
         <v>0.1232575868346753</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.3554135156808968</v>
+        <v>-0.3554135156808967</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>REER_within</t>
         </is>
@@ -1385,7 +1373,7 @@
         <v>-0.1024043659453598</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1004251385788368</v>
+        <v>0.1004251385788369</v>
       </c>
       <c r="D12" t="n">
         <v>0.005108225149678319</v>
@@ -1397,25 +1385,25 @@
         <v>0.12874803740802</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.05082317139641967</v>
+        <v>-0.0508231713964197</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.03354948048175851</v>
+        <v>-0.03354948048175853</v>
       </c>
       <c r="I12" t="n">
         <v>0.005970193834536096</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02545801417043</v>
+        <v>-0.02545801417043001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1279613376987077</v>
+        <v>0.1279613376987078</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09880215935990673</v>
+        <v>-0.09880215935990674</v>
       </c>
       <c r="N12" t="n">
         <v>0.06554396536486934</v>
@@ -1436,53 +1424,53 @@
         <v>0.1340921381093569</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08412460309788325</v>
+        <v>-0.08412460309788326</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07716650280402285</v>
+        <v>-0.07716650280402287</v>
       </c>
       <c r="V12" t="n">
-        <v>0.007673957990210671</v>
+        <v>0.007673957990210665</v>
       </c>
       <c r="W12" t="n">
         <v>-0.03656910482440823</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1393634145288249</v>
+        <v>0.139363414528825</v>
       </c>
       <c r="Y12" t="n">
         <v>0.8860995008822057</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.08921420943400357</v>
+        <v>-0.08921420943400354</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>SH_within</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9787963686249099</v>
+        <v>0.9787963686249103</v>
       </c>
       <c r="C13" t="n">
         <v>-0.728801119542662</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7592871856560741</v>
+        <v>-0.7592871856560743</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1140672766905316</v>
+        <v>-0.1140672766905315</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3548747588492231</v>
+        <v>-0.354874758849223</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5531083869641533</v>
+        <v>0.5531083869641534</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1140369328089865</v>
+        <v>-0.1140369328089864</v>
       </c>
       <c r="I13" t="n">
         <v>-0.1900798992435649</v>
@@ -1494,25 +1482,25 @@
         <v>-0.3534845838879406</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.09880215935990673</v>
+        <v>-0.09880215935990674</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7689006876823686</v>
+        <v>-0.7689006876823685</v>
       </c>
       <c r="O13" t="n">
         <v>0.9092203471461499</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7580096931887702</v>
+        <v>-0.7580096931887701</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.7723638800776218</v>
+        <v>-0.7723638800776217</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.05054821081842297</v>
+        <v>-0.050548210818423</v>
       </c>
       <c r="S13" t="n">
         <v>-0.3586501380271057</v>
@@ -1524,13 +1512,13 @@
         <v>-0.1812686511095614</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2301679459615957</v>
+        <v>-0.2301679459615956</v>
       </c>
       <c r="W13" t="n">
         <v>-0.1832802757957847</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3599097234496677</v>
+        <v>-0.3599097234496675</v>
       </c>
       <c r="Y13" t="n">
         <v>-0.1068988745802539</v>
@@ -1540,34 +1528,34 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>trend_within</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.7399368851371887</v>
+        <v>-0.7399368851371885</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9715445987291108</v>
+        <v>0.9715445987291107</v>
       </c>
       <c r="D14" t="n">
         <v>0.9773789413615545</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0437052829348609</v>
+        <v>-0.04370528293486092</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5082235787439886</v>
+        <v>0.5082235787439884</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7308397985224826</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3020017191253656</v>
+        <v>0.3020017191253655</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2203872848496002</v>
+        <v>0.2203872848496001</v>
       </c>
       <c r="J14" t="n">
         <v>0.1997287231143273</v>
@@ -1579,7 +1567,7 @@
         <v>0.06554396536486934</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7689006876823686</v>
+        <v>-0.7689006876823685</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1594,19 +1582,19 @@
         <v>0.9773895096582289</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.05839790573699311</v>
+        <v>-0.0583979057369932</v>
       </c>
       <c r="S14" t="n">
         <v>0.5097561235504374</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7327386713463642</v>
+        <v>-0.7327386713463643</v>
       </c>
       <c r="U14" t="n">
         <v>0.3270285643996672</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2478764637189371</v>
+        <v>0.247876463718937</v>
       </c>
       <c r="W14" t="n">
         <v>0.2236291007542996</v>
@@ -1615,14 +1603,14 @@
         <v>0.5336413935285641</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.07468965976102042</v>
+        <v>0.07468965976102043</v>
       </c>
       <c r="Z14" t="n">
         <v>-0.7585983988856677</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>i_lag1_within</t>
         </is>
@@ -1631,28 +1619,28 @@
         <v>0.9197151451857176</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.6910013869912225</v>
+        <v>-0.6910013869912226</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7168417244309265</v>
+        <v>-0.7168417244309264</v>
       </c>
       <c r="E15" t="n">
         <v>-0.154743663702222</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3476005160648407</v>
+        <v>-0.3476005160648406</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5249199428257839</v>
+        <v>0.5249199428257838</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01847722106656332</v>
+        <v>-0.01847722106656333</v>
       </c>
       <c r="I15" t="n">
         <v>-0.1145316919028703</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1254979587604979</v>
+        <v>-0.125497958760498</v>
       </c>
       <c r="K15" t="n">
         <v>-0.3447427022394846</v>
@@ -1673,7 +1661,7 @@
         <v>-0.7056183013745686</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7183453061060086</v>
+        <v>-0.7183453061060083</v>
       </c>
       <c r="R15" t="n">
         <v>-0.1013064213213598</v>
@@ -1704,7 +1692,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P_lag1_within</t>
         </is>
@@ -1713,10 +1701,10 @@
         <v>-0.7480039915943725</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9992334893105516</v>
+        <v>0.9992334893105513</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9385846196643306</v>
+        <v>0.9385846196643308</v>
       </c>
       <c r="E16" t="n">
         <v>-0.157581973292429</v>
@@ -1743,7 +1731,7 @@
         <v>0.09533674564891652</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7580096931887702</v>
+        <v>-0.7580096931887701</v>
       </c>
       <c r="N16" t="n">
         <v>0.9715654991370156</v>
@@ -1755,13 +1743,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9390239323274787</v>
+        <v>0.9390239323274785</v>
       </c>
       <c r="R16" t="n">
         <v>-0.1945265961984419</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4754278155554195</v>
+        <v>0.4754278155554196</v>
       </c>
       <c r="T16" t="n">
         <v>-0.7466351862291553</v>
@@ -1770,7 +1758,7 @@
         <v>0.385269576652625</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2580717059594525</v>
+        <v>0.2580717059594526</v>
       </c>
       <c r="W16" t="n">
         <v>0.2164563445281057</v>
@@ -1782,26 +1770,26 @@
         <v>0.1071619214425534</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.7188650810050853</v>
+        <v>-0.7188650810050852</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>W_lag1_within</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.7410177579100143</v>
+        <v>-0.7410177579100142</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9380683044644278</v>
+        <v>0.9380683044644277</v>
       </c>
       <c r="D17" t="n">
         <v>0.9990738433927511</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07168818355430046</v>
+        <v>0.07168818355430047</v>
       </c>
       <c r="F17" t="n">
         <v>0.5325634258718589</v>
@@ -1813,7 +1801,7 @@
         <v>0.2302234040128481</v>
       </c>
       <c r="I17" t="n">
-        <v>0.179114032050075</v>
+        <v>0.1791140320500751</v>
       </c>
       <c r="J17" t="n">
         <v>0.2021994211061201</v>
@@ -1825,16 +1813,16 @@
         <v>-0.008590278381261912</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7723638800776218</v>
+        <v>-0.7723638800776217</v>
       </c>
       <c r="N17" t="n">
         <v>0.9773895096582289</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7183453061060086</v>
+        <v>-0.7183453061060083</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9390239323274787</v>
+        <v>0.9390239323274785</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1855,20 +1843,20 @@
         <v>0.2280033384855084</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2317115865771955</v>
+        <v>0.2317115865771956</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5474159524007333</v>
+        <v>0.5474159524007332</v>
       </c>
       <c r="Y17" t="n">
         <v>0.01218255224795026</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.7488232193002459</v>
+        <v>-0.7488232193002458</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WR_lag1_within</t>
         </is>
@@ -1877,25 +1865,25 @@
         <v>-0.0344189024565565</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2046524560409182</v>
+        <v>-0.2046524560409183</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04505610243589216</v>
+        <v>0.04505610243589214</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9826798363442868</v>
+        <v>0.9826798363442869</v>
       </c>
       <c r="F18" t="n">
         <v>0.1312563999114845</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4424657956539679</v>
+        <v>0.442465795653968</v>
       </c>
       <c r="H18" t="n">
         <v>-0.2202120339728879</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05914136800731865</v>
+        <v>0.05914136800731867</v>
       </c>
       <c r="J18" t="n">
         <v>0.1353098119635215</v>
@@ -1907,10 +1895,10 @@
         <v>-0.1917461894727745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.05054821081842297</v>
+        <v>-0.050548210818423</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05839790573699311</v>
+        <v>-0.0583979057369932</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1013064213213598</v>
@@ -1934,7 +1922,7 @@
         <v>-0.2255530421022408</v>
       </c>
       <c r="V18" t="n">
-        <v>0.09247853424479781</v>
+        <v>0.09247853424479778</v>
       </c>
       <c r="W18" t="n">
         <v>0.1531009378991794</v>
@@ -1950,7 +1938,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>GDP_lag1_within</t>
         </is>
@@ -1968,16 +1956,16 @@
         <v>0.1464936116249397</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9984926731230138</v>
+        <v>0.9984926731230139</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2713902907614898</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0271662516839218</v>
+        <v>0.02716625168392179</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1350122444071746</v>
+        <v>0.1350122444071745</v>
       </c>
       <c r="J19" t="n">
         <v>0.3874832285587649</v>
@@ -1998,7 +1986,7 @@
         <v>-0.3459320805657979</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4754278155554195</v>
+        <v>0.4754278155554196</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5359456605321472</v>
@@ -2010,19 +1998,19 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2734638112805821</v>
+        <v>-0.273463811280582</v>
       </c>
       <c r="U19" t="n">
         <v>0.0514855449344607</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2116062012979009</v>
+        <v>0.211606201297901</v>
       </c>
       <c r="W19" t="n">
         <v>0.4200085906432997</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9633061392348433</v>
+        <v>0.9633061392348434</v>
       </c>
       <c r="Y19" t="n">
         <v>0.1242662215266728</v>
@@ -2032,16 +2020,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>LS_lag1_within</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5665057825466118</v>
+        <v>0.566505782546612</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.7461294287412867</v>
+        <v>-0.7461294287412865</v>
       </c>
       <c r="D20" t="n">
         <v>-0.6601564091632525</v>
@@ -2053,13 +2041,13 @@
         <v>-0.270889983805397</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9523127648794044</v>
+        <v>0.9523127648794043</v>
       </c>
       <c r="H20" t="n">
         <v>-0.1998627058426368</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1241029135023845</v>
+        <v>-0.1241029135023844</v>
       </c>
       <c r="J20" t="n">
         <v>-0.1646701362559276</v>
@@ -2068,13 +2056,13 @@
         <v>-0.2847098167428029</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.08412460309788325</v>
+        <v>-0.08412460309788326</v>
       </c>
       <c r="M20" t="n">
         <v>0.5720929078121144</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7327386713463642</v>
+        <v>-0.7327386713463643</v>
       </c>
       <c r="O20" t="n">
         <v>0.5395310360181331</v>
@@ -2089,7 +2077,7 @@
         <v>0.4259254204146974</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2734638112805821</v>
+        <v>-0.273463811280582</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2104,17 +2092,17 @@
         <v>-0.2343022258856159</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2825323155089775</v>
+        <v>-0.2825323155089776</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.04957094979656468</v>
+        <v>-0.04957094979656467</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.546102626491488</v>
+        <v>0.5461026264914881</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>UN_lag1_within</t>
         </is>
@@ -2123,7 +2111,7 @@
         <v>-0.183496321026466</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3805927874327037</v>
+        <v>0.3805927874327036</v>
       </c>
       <c r="D21" t="n">
         <v>0.2753731258369863</v>
@@ -2135,7 +2123,7 @@
         <v>0.05200941674030939</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.390925988115669</v>
+        <v>-0.3909259881156689</v>
       </c>
       <c r="H21" t="n">
         <v>0.9387681744519389</v>
@@ -2150,7 +2138,7 @@
         <v>0.07944270331839708</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07716650280402285</v>
+        <v>-0.07716650280402287</v>
       </c>
       <c r="M21" t="n">
         <v>-0.1812686511095614</v>
@@ -2183,10 +2171,10 @@
         <v>0.299006061816376</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5185392667648814</v>
+        <v>0.5185392667648813</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08231930413646282</v>
+        <v>0.08231930413646281</v>
       </c>
       <c r="Y21" t="n">
         <v>-0.03146250380574283</v>
@@ -2196,7 +2184,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>SHORTUN_lag1_within</t>
         </is>
@@ -2208,52 +2196,52 @@
         <v>0.2530410743735391</v>
       </c>
       <c r="D22" t="n">
-        <v>0.22826504286999</v>
+        <v>0.2282650428699901</v>
       </c>
       <c r="E22" t="n">
         <v>0.1044313972669975</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2113956695133399</v>
+        <v>0.21139566951334</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2077225269364404</v>
+        <v>-0.2077225269364405</v>
       </c>
       <c r="H22" t="n">
         <v>0.2915178820472308</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7965892936420816</v>
+        <v>0.796589293642082</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6757077905928681</v>
+        <v>0.675707790592868</v>
       </c>
       <c r="K22" t="n">
         <v>0.3174167359269896</v>
       </c>
       <c r="L22" t="n">
-        <v>0.007673957990210671</v>
+        <v>0.007673957990210665</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2301679459615957</v>
+        <v>-0.2301679459615956</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2478764637189371</v>
+        <v>0.247876463718937</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1999761762835634</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2580717059594525</v>
+        <v>0.2580717059594526</v>
       </c>
       <c r="Q22" t="n">
         <v>0.2280033384855084</v>
       </c>
       <c r="R22" t="n">
-        <v>0.09247853424479781</v>
+        <v>0.09247853424479778</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2116062012979009</v>
+        <v>0.211606201297901</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1680690302958924</v>
@@ -2268,17 +2256,17 @@
         <v>0.5984787210290026</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3327980883891194</v>
+        <v>0.3327980883891195</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.01467892652904522</v>
+        <v>0.0146789265290452</v>
       </c>
       <c r="Z22" t="n">
         <v>-0.2034870145681784</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>LONGUN_lag1_within</t>
         </is>
@@ -2305,13 +2293,13 @@
         <v>0.4397169429861426</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3853032059775952</v>
+        <v>0.3853032059775953</v>
       </c>
       <c r="J23" t="n">
         <v>0.9018633145039019</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4164659717263127</v>
+        <v>0.4164659717263126</v>
       </c>
       <c r="L23" t="n">
         <v>-0.03656910482440823</v>
@@ -2329,7 +2317,7 @@
         <v>0.2164563445281057</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2317115865771955</v>
+        <v>0.2317115865771956</v>
       </c>
       <c r="R23" t="n">
         <v>0.1531009378991794</v>
@@ -2341,7 +2329,7 @@
         <v>-0.2343022258856159</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5185392667648814</v>
+        <v>0.5185392667648813</v>
       </c>
       <c r="V23" t="n">
         <v>0.5984787210290026</v>
@@ -2353,14 +2341,14 @@
         <v>0.4318237602204008</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.0268776998976795</v>
+        <v>-0.02687769989767948</v>
       </c>
       <c r="Z23" t="n">
         <v>-0.1835825498326374</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>LF_lag1_within</t>
         </is>
@@ -2369,7 +2357,7 @@
         <v>-0.3523125450335107</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5060389634123369</v>
+        <v>0.5060389634123368</v>
       </c>
       <c r="D24" t="n">
         <v>0.5488741722992444</v>
@@ -2396,10 +2384,10 @@
         <v>0.9975287621035562</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1393634145288249</v>
+        <v>0.139363414528825</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3599097234496677</v>
+        <v>-0.3599097234496675</v>
       </c>
       <c r="N24" t="n">
         <v>0.5336413935285641</v>
@@ -2411,22 +2399,22 @@
         <v>0.5054246079428787</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5474159524007333</v>
+        <v>0.5474159524007332</v>
       </c>
       <c r="R24" t="n">
         <v>0.1386038610445589</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9633061392348433</v>
+        <v>0.9633061392348434</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2825323155089775</v>
+        <v>-0.2825323155089776</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08231930413646282</v>
+        <v>0.08231930413646281</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3327980883891194</v>
+        <v>0.3327980883891195</v>
       </c>
       <c r="W24" t="n">
         <v>0.4318237602204008</v>
@@ -2442,37 +2430,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>REER_lag1_within</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1085412725392239</v>
+        <v>-0.1085412725392238</v>
       </c>
       <c r="C25" t="n">
         <v>0.1022002569754112</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01752667053921757</v>
+        <v>0.01752667053921759</v>
       </c>
       <c r="E25" t="n">
         <v>-0.149849644306802</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1242403715666645</v>
+        <v>0.1242403715666644</v>
       </c>
       <c r="G25" t="n">
         <v>-0.03740792660327314</v>
       </c>
       <c r="H25" t="n">
-        <v>0.014878133535407</v>
+        <v>0.01487813353540698</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01288808054943055</v>
+        <v>0.01288808054943057</v>
       </c>
       <c r="J25" t="n">
-        <v>0.003373045331640988</v>
+        <v>0.003373045331640987</v>
       </c>
       <c r="K25" t="n">
         <v>0.1232575868346753</v>
@@ -2484,7 +2472,7 @@
         <v>-0.1068988745802539</v>
       </c>
       <c r="N25" t="n">
-        <v>0.07468965976102042</v>
+        <v>0.07468965976102043</v>
       </c>
       <c r="O25" t="n">
         <v>-0.1094383639087107</v>
@@ -2502,16 +2490,16 @@
         <v>0.1242662215266728</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.04957094979656468</v>
+        <v>-0.04957094979656467</v>
       </c>
       <c r="U25" t="n">
         <v>-0.03146250380574283</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01467892652904522</v>
+        <v>0.0146789265290452</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.0268776998976795</v>
+        <v>-0.02687769989767948</v>
       </c>
       <c r="X25" t="n">
         <v>0.1245463254121493</v>
@@ -2524,19 +2512,19 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>SH_lag1_within</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9109655048595507</v>
+        <v>0.9109655048595505</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.7050554225057321</v>
+        <v>-0.7050554225057319</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7474713554899223</v>
+        <v>-0.7474713554899222</v>
       </c>
       <c r="E26" t="n">
         <v>-0.161536225260997</v>
@@ -2548,7 +2536,7 @@
         <v>0.5316360213141197</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.01975413508918413</v>
+        <v>-0.01975413508918411</v>
       </c>
       <c r="I26" t="n">
         <v>-0.1206258957207637</v>
@@ -2557,10 +2545,10 @@
         <v>-0.1249004035366156</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3554135156808968</v>
+        <v>-0.3554135156808967</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.08921420943400357</v>
+        <v>-0.08921420943400354</v>
       </c>
       <c r="M26" t="n">
         <v>0.9352119757865613</v>
@@ -2572,10 +2560,10 @@
         <v>0.9829321240525881</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7188650810050853</v>
+        <v>-0.7188650810050852</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.7488232193002459</v>
+        <v>-0.7488232193002458</v>
       </c>
       <c r="R26" t="n">
         <v>-0.1099722096599096</v>
@@ -2584,7 +2572,7 @@
         <v>-0.3601258375209087</v>
       </c>
       <c r="T26" t="n">
-        <v>0.546102626491488</v>
+        <v>0.5461026264914881</v>
       </c>
       <c r="U26" t="n">
         <v>-0.1329449816536053</v>
